--- a/Current TAPPs/LA-Q-ICP-MS_TAPP_v71.xlsx
+++ b/Current TAPPs/LA-Q-ICP-MS_TAPP_v71.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -603,7 +603,7 @@
           <t>Keyed By</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
@@ -798,7 +798,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="1" t="n"/>
       <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -897,7 +897,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="1" t="n"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -996,7 +996,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="1" t="n"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1095,7 +1095,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="1" t="n"/>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1194,7 +1194,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="1" t="n"/>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1293,7 +1293,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="1" t="n"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1392,7 +1392,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="1" t="n"/>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1491,7 +1491,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="1" t="n"/>
       <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1590,7 +1590,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Encourages formal procedure registration and ensures traceability.</t>
         </is>
@@ -1689,7 +1689,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session, which may cover several samples, and this is the link back to the raw instrument files.</t>
         </is>
@@ -1768,7 +1768,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="1" t="n"/>
       <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1867,7 +1867,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="1" t="n"/>
       <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1966,7 +1966,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="1" t="n"/>
       <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2065,7 +2065,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="1" t="n"/>
       <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2164,7 +2164,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="1" t="n"/>
       <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2263,7 +2263,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="1" t="n"/>
       <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2362,7 +2362,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>Provides a stable, citable link to the companion method independent of whether a dataset has been deposited.</t>
         </is>
@@ -2465,7 +2465,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="1" t="n"/>
       <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2620,7 +2620,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>Used for discoverability and procedure matching, and because the material type constrains sample preparation, calibration and matrix-matching requirements.</t>
         </is>
@@ -2723,7 +2723,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
+      <c r="J24" s="1" t="n"/>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2822,7 +2822,7 @@
           <t>defines: sample</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session and may cover several samples.</t>
         </is>
@@ -2925,7 +2925,7 @@
           <t>defines: sampling unit</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="1" t="n"/>
       <c r="K26" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3000,7 +3000,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
+      <c r="J27" s="1" t="n"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3099,7 +3099,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="1" t="n"/>
       <c r="K28" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3198,7 +3198,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n"/>
+      <c r="J29" s="1" t="n"/>
       <c r="K29" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3297,7 +3297,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>In mapping the large area ablated averages out surface effects.</t>
         </is>
@@ -3396,7 +3396,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="1" t="n"/>
       <c r="K31" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3467,7 +3467,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
+      <c r="J32" s="1" t="n"/>
       <c r="K32" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3598,7 +3598,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n"/>
+      <c r="J35" s="1" t="n"/>
       <c r="K35" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3697,7 +3697,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>Recording it as a controlled value lets procedures be found by vendor.</t>
         </is>
@@ -3776,7 +3776,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="n"/>
+      <c r="J37" s="1" t="n"/>
       <c r="K37" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3875,7 +3875,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Determines available cell configurations and interference mitigation strategies.</t>
         </is>
@@ -3978,7 +3978,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>Supports traceability to instrument service records.</t>
         </is>
@@ -4081,7 +4081,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>Some instruments offer multiple skimmer cone geometries (standard, high-sensitivity) that differ in aperture size and affect ion transmission efficiency and matrix tolerance.</t>
         </is>
@@ -4184,7 +4184,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>Cone material affects sensitivity, matrix tolerance, and long-term stability.</t>
         </is>
@@ -4263,7 +4263,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>Affects ion transmission efficiency, oxide formation, and doubly-charged species production.</t>
         </is>
@@ -4342,7 +4342,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>Injector inner diameter (typically 1.5–2.5 mm) affects aerosol transport efficiency and plasma conditions in LA-ICP-MS.</t>
         </is>
@@ -4445,7 +4445,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>Capacitively decouples the plasma from the load coil, reducing secondary discharge and improving ion extraction efficiency.</t>
         </is>
@@ -4548,7 +4548,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>For quadrupole instruments this is fixed at unit resolution by instrument design.</t>
         </is>
@@ -4647,7 +4647,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n"/>
+      <c r="J46" s="1" t="n"/>
       <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4746,7 +4746,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>On MS/MS instruments a second mass filter preceding the cell enables precursor-ion selection.</t>
         </is>
@@ -4849,7 +4849,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J48" s="2" t="n"/>
+      <c r="J48" s="1" t="n"/>
       <c r="K48" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4948,7 +4948,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n"/>
+      <c r="J49" s="1" t="n"/>
       <c r="K49" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5047,7 +5047,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J50" s="2" t="n"/>
+      <c r="J50" s="1" t="n"/>
       <c r="K50" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5146,7 +5146,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
         <is>
           <t>Cell volume is a primary determinant of aerosol washout time and therefore the achievable time resolution of the data.</t>
         </is>
@@ -5249,7 +5249,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n"/>
+      <c r="J52" s="1" t="n"/>
       <c r="K52" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5384,7 +5384,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr">
         <is>
           <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability. Ensures every procedure record is self-describing and comparable across the library.</t>
         </is>
@@ -5463,7 +5463,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J56" s="2" t="n"/>
+      <c r="J56" s="1" t="n"/>
       <c r="K56" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5562,7 +5562,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
         <is>
           <t>Measured companion to Laser Spot Geometry: nominal and delivered spot size can differ appreciably with optics condition and focus.</t>
         </is>
@@ -5641,7 +5641,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J58" s="2" t="n"/>
+      <c r="J58" s="1" t="n"/>
       <c r="K58" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5740,7 +5740,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
         <is>
           <t>Less commonly reported than fluence because it does not account for spot area.</t>
         </is>
@@ -5843,7 +5843,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
         <is>
           <t>Fluence is the physically meaningful quantity controlling ablation rate, crater morphology, elemental fractionation, and particle size distribution.</t>
         </is>
@@ -5946,7 +5946,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr">
         <is>
           <t>A flat-top (top-hat) profile produces more uniform ablation craters and more reproducible crater morphology than a Gaussian beam.</t>
         </is>
@@ -6049,7 +6049,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr">
         <is>
           <t>For mapping methods, repetition rate together with scan speed and spot size determines pixel size and spatial resolution.</t>
         </is>
@@ -6152,7 +6152,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr">
         <is>
           <t>Pulse duration determines the ablation regime: nanosecond (ns) pulses involve significant thermal effects and elemental fractionation; femtosecond (fs) pulses are non-thermal and substantially reduce elemental fractionation and matrix effects.</t>
         </is>
@@ -6255,7 +6255,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="1" t="inlineStr">
         <is>
           <t>For spot analysis, reflects the deliberate trade-off between signal accumulation (longer = lower LOD), sample consumption, and session throughput.</t>
         </is>
@@ -6358,7 +6358,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
         <is>
           <t>Sets the achievable depth resolution and governs downhole elemental fractionation.</t>
         </is>
@@ -6437,7 +6437,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="1" t="inlineStr">
         <is>
           <t>Together with spot size and repetition rate, determines spatial resolution along the scan direction.</t>
         </is>
@@ -6540,7 +6540,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="1" t="inlineStr">
         <is>
           <t>Together with spot size, this determines whether adjacent lines are contiguous (line spacing = spot size), overlapping (line spacing &lt; spot size), or have gaps (line spacing &gt; spot size).</t>
         </is>
@@ -6643,7 +6643,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="1" t="inlineStr">
         <is>
           <t>Helium is standard for most UV laser systems due to superior aerosol transport.</t>
         </is>
@@ -6746,7 +6746,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="1" t="inlineStr">
         <is>
           <t>Argon make-up is standard and maintains total gas delivery where the carrier flow alone is insufficient — downstream of an ablation cell, or of a desolvation system that has removed solvent load. Small nitrogen or hydrogen additions enhance sensitivity for some elements.</t>
         </is>
@@ -6849,7 +6849,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="1" t="inlineStr">
         <is>
           <t>Determines plasma volume and stability.</t>
         </is>
@@ -6952,7 +6952,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J71" s="1" t="inlineStr">
         <is>
           <t>Affects ion extraction efficiency and oxide production rates.</t>
         </is>
@@ -7055,7 +7055,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J72" s="1" t="inlineStr">
         <is>
           <t>Affects plasma temperature, ionisation efficiency, oxide formation, and whether cool or normal plasma conditions are in effect.</t>
         </is>
@@ -7158,7 +7158,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J73" s="1" t="inlineStr">
         <is>
           <t>Cool plasma substantially reduces argide-based polyatomic interferences (e.g., ⁴⁰Ar on ⁴⁰Ca, ⁴⁰Ar⁴⁰Ar on ⁸⁰Se). A fundamental method design choice that determines which interference corrections are necessary.</t>
         </is>
@@ -7261,7 +7261,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J74" s="1" t="inlineStr">
         <is>
           <t>Note: active signal smoothing devices (e.g., squid, SCFAST) are generally incompatible with high-resolution raster mapping because they degrade spatial resolution by mixing aerosol from successive laser shots.</t>
         </is>
@@ -7364,7 +7364,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J75" s="2" t="n"/>
+      <c r="J75" s="1" t="n"/>
       <c r="K75" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7463,7 +7463,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="1" t="inlineStr">
         <is>
           <t>Useful yield is the more comparable of the two wherever the amount of material consumed varies between procedures, as it does with spot size, fluence and repetition rate.</t>
         </is>
@@ -7542,7 +7542,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J77" s="2" t="n"/>
+      <c r="J77" s="1" t="n"/>
       <c r="K77" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7641,7 +7641,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="1" t="n"/>
       <c r="K78" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7736,7 +7736,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J79" s="1" t="inlineStr">
         <is>
           <t>Doubly-charged ions appear at half the mass of the parent ion and can cause isobaric interferences on analytes in that mass region.</t>
         </is>
@@ -7811,7 +7811,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J80" s="2" t="n"/>
+      <c r="J80" s="1" t="n"/>
       <c r="K80" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7886,7 +7886,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J81" s="2" t="n"/>
+      <c r="J81" s="1" t="n"/>
       <c r="K81" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7985,7 +7985,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J82" s="2" t="n"/>
+      <c r="J82" s="1" t="n"/>
       <c r="K82" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8084,7 +8084,7 @@
           <t>defines: analyte</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n"/>
+      <c r="J83" s="1" t="n"/>
       <c r="K83" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8179,7 +8179,7 @@
           <t>defines: channel per analyte</t>
         </is>
       </c>
-      <c r="J84" s="2" t="n"/>
+      <c r="J84" s="1" t="n"/>
       <c r="K84" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8278,7 +8278,7 @@
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J85" s="1" t="inlineStr">
         <is>
           <t>A procedure may acquire many channels and report a small number of derived quantities; without this field a data consumer cannot tell which.</t>
         </is>
@@ -8353,7 +8353,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J86" s="1" t="inlineStr">
         <is>
           <t>Peak hopping is standard for multi-element trace analysis as it maximises integration time at each mass.</t>
         </is>
@@ -8456,7 +8456,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J87" s="2" t="n"/>
+      <c r="J87" s="1" t="n"/>
       <c r="K87" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8531,7 +8531,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="J88" s="1" t="inlineStr">
         <is>
           <t>Helium (He) is the standard collision gas for kinetic energy discrimination, being low in mass and chemically inert.</t>
         </is>
@@ -8634,7 +8634,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="J89" s="1" t="inlineStr">
         <is>
           <t>Controls the degree of ion thermalization and KED efficiency; higher flow rates give greater interference suppression at the cost of analyte sensitivity.</t>
         </is>
@@ -8737,7 +8737,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="J90" s="1" t="inlineStr">
         <is>
           <t>A negative bias preferentially retards slow polyatomic ions while transmitting faster analyte ions, controlling the degree of polyatomic suppression.</t>
         </is>
@@ -8840,7 +8840,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J91" s="2" t="n"/>
+      <c r="J91" s="1" t="n"/>
       <c r="K91" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8939,7 +8939,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J92" s="2" t="n"/>
+      <c r="J92" s="1" t="n"/>
       <c r="K92" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9038,7 +9038,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J93" s="1" t="inlineStr">
         <is>
           <t>The proportions change reaction efficiency and interference suppression independently of which gases are used.</t>
         </is>
@@ -9141,7 +9141,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n"/>
+      <c r="J94" s="1" t="n"/>
       <c r="K94" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9236,7 +9236,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J95" s="1" t="inlineStr">
         <is>
           <t>Longer dwell times improve counting statistics and lower detection limits but reduce the number of isotopes measurable within a given scan cycle time. For mapping, scan cycle time directly determines spatial resolution at a given scan speed: shorter cycle time = finer spatial resolution.</t>
         </is>
@@ -9335,7 +9335,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J96" s="1" t="inlineStr">
         <is>
           <t>Sets the time resolution of the downhole signal.</t>
         </is>
@@ -9414,7 +9414,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J97" s="2" t="n"/>
+      <c r="J97" s="1" t="n"/>
       <c r="K97" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9513,7 +9513,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J98" s="2" t="n"/>
+      <c r="J98" s="1" t="n"/>
       <c r="K98" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9612,7 +9612,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J99" s="1" t="inlineStr">
         <is>
           <t>Enables spatial reconstruction and co-registration with other analytical images.</t>
         </is>
@@ -9711,7 +9711,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J100" s="2" t="n"/>
+      <c r="J100" s="1" t="n"/>
       <c r="K100" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9810,7 +9810,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J101" s="1" t="inlineStr">
         <is>
           <t>Depends on the size of the feature of interest rather than being fixed in the procedure.</t>
         </is>
@@ -9913,7 +9913,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J102" s="1" t="inlineStr">
         <is>
           <t>The map area depends on the size of the grain or phase to be mapped.</t>
         </is>
@@ -10076,7 +10076,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J105" s="1" t="inlineStr">
         <is>
           <t>Corrects for variable ablation yield between analyses.</t>
         </is>
@@ -10179,7 +10179,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n"/>
+      <c r="J106" s="1" t="n"/>
       <c r="K106" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10278,7 +10278,7 @@
           <t>analyte</t>
         </is>
       </c>
-      <c r="J107" s="2" t="n"/>
+      <c r="J107" s="1" t="n"/>
       <c r="K107" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10353,7 +10353,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J108" s="2" t="n"/>
+      <c r="J108" s="1" t="n"/>
       <c r="K108" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10448,7 +10448,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J109" s="2" t="n"/>
+      <c r="J109" s="1" t="n"/>
       <c r="K109" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10523,7 +10523,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J110" s="1" t="inlineStr">
         <is>
           <t>A reported uncertainty is not interpretable without it: the same numeric value means different things at 1-sigma and at 95% confidence.</t>
         </is>
@@ -10602,7 +10602,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J111" s="2" t="n"/>
+      <c r="J111" s="1" t="n"/>
       <c r="K111" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10701,7 +10701,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J112" s="2" t="n"/>
+      <c r="J112" s="1" t="n"/>
       <c r="K112" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10800,7 +10800,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J113" s="2" t="n"/>
+      <c r="J113" s="1" t="n"/>
       <c r="K113" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10899,7 +10899,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J114" s="1" t="inlineStr">
         <is>
           <t>It is equal to or shorter than the Ablation Duration per Spot because the signal start and end transients are typically discarded.</t>
         </is>
@@ -11002,7 +11002,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J115" s="2" t="n"/>
+      <c r="J115" s="1" t="n"/>
       <c r="K115" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11101,7 +11101,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J116" s="2" t="n"/>
+      <c r="J116" s="1" t="n"/>
       <c r="K116" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11196,7 +11196,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J117" s="2" t="n"/>
+      <c r="J117" s="1" t="n"/>
       <c r="K117" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11295,7 +11295,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J118" s="2" t="n"/>
+      <c r="J118" s="1" t="n"/>
       <c r="K118" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11394,7 +11394,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J119" s="2" t="n"/>
+      <c r="J119" s="1" t="n"/>
       <c r="K119" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11493,7 +11493,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J120" s="2" t="n"/>
+      <c r="J120" s="1" t="n"/>
       <c r="K120" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11592,7 +11592,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J121" s="2" t="n"/>
+      <c r="J121" s="1" t="n"/>
       <c r="K121" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11691,7 +11691,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J122" s="2" t="n"/>
+      <c r="J122" s="1" t="n"/>
       <c r="K122" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11790,7 +11790,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J123" s="2" t="n"/>
+      <c r="J123" s="1" t="n"/>
       <c r="K123" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11885,7 +11885,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J124" s="2" t="n"/>
+      <c r="J124" s="1" t="n"/>
       <c r="K124" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11956,7 +11956,7 @@
           <t>analyte</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="J125" s="1" t="inlineStr">
         <is>
           <t>Follows the criterion-versus-measurement split the library applies wherever a procedure sets a threshold and an analysis reports a value against it.</t>
         </is>
@@ -12031,7 +12031,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J126" s="1" t="inlineStr">
         <is>
           <t>Criteria and outcome are combined in one field because neither is interpretable without the other, following the precision/accuracy precedent.</t>
         </is>
@@ -12110,7 +12110,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J127" s="2" t="n"/>
+      <c r="J127" s="1" t="n"/>
       <c r="K127" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12245,7 +12245,7 @@
           <t>analyte</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J130" s="1" t="inlineStr">
         <is>
           <t>Results calibrated against different published values for the same material are not directly comparable.</t>
         </is>
@@ -12348,7 +12348,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="J131" s="1" t="inlineStr">
         <is>
           <t>For LA-ICP-MS, this defines the bracketing interval between calibration standard ablations used to monitor and correct for instrumental drift.</t>
         </is>
@@ -12451,7 +12451,7 @@
           <t>defines: standard</t>
         </is>
       </c>
-      <c r="J132" s="2" t="n"/>
+      <c r="J132" s="1" t="n"/>
       <c r="K132" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12550,7 +12550,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J133" s="2" t="n"/>
+      <c r="J133" s="1" t="n"/>
       <c r="K133" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12649,7 +12649,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J134" s="2" t="n"/>
+      <c r="J134" s="1" t="n"/>
       <c r="K134" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12748,7 +12748,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J135" s="1" t="inlineStr">
         <is>
           <t>Concentrations between LOD and LOQ are detectable but not reliably quantifiable.</t>
         </is>
@@ -12851,7 +12851,7 @@
           <t>sample &gt; sampling unit x reported property</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J136" s="1" t="inlineStr">
         <is>
           <t>Where a procedure reports both, agreement indicates the measurement is shot-noise limited, and a larger observed scatter indicates a further source of variance.</t>
         </is>
@@ -12954,7 +12954,7 @@
           <t>sample &gt; sampling unit x reported property</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J137" s="1" t="inlineStr">
         <is>
           <t>This is the finest of the three precision levels the library records, below within-session and between-session precision: it describes the repeatability of one analysis rather than agreement between analyses, and is normally the smallest of the three.</t>
         </is>
@@ -13057,7 +13057,7 @@
           <t>standard x reported property</t>
         </is>
       </c>
-      <c r="J138" s="2" t="n"/>
+      <c r="J138" s="1" t="n"/>
       <c r="K138" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13156,7 +13156,7 @@
           <t>standard x reported property</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J139" s="1" t="inlineStr">
         <is>
           <t>Long-term precision is normally poorer than within-session precision and is the figure a data user should carry when comparing results from different sessions.</t>
         </is>
@@ -13259,7 +13259,7 @@
           <t>standard x reported property</t>
         </is>
       </c>
-      <c r="J140" s="2" t="n"/>
+      <c r="J140" s="1" t="n"/>
       <c r="K140" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13355,7 +13355,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J142" s="1" t="inlineStr">
         <is>
           <t>Answers whether a reported aggregate is defensible as a single population. The value cannot be known before the analysis.</t>
         </is>
@@ -13430,7 +13430,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J143" s="2" t="n"/>
+      <c r="J143" s="1" t="n"/>
       <c r="K143" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13494,7 +13494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -13618,7 +13618,7 @@
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Spot</t>
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
@@ -13626,7 +13626,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Spot</t>
+          <t>Transect</t>
         </is>
       </c>
       <c r="B10" s="1" t="n"/>
@@ -13634,298 +13634,290 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Transect</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="B11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Mapping</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n"/>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>This field applies to this analytical mode and should be reported.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>This field applies to this analytical mode and should be reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
           <t>This field does not apply to this analytical mode.</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>What to enter</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>What to enter</t>
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>Controlled list</t>
+          <t>Controlled list / Text</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
+          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>Controlled list / Text</t>
+          <t>Numeric (unit)</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
+          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Numeric (unit)</t>
+          <t>Numeric + unit</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
+          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Numeric + unit</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
+          <t>Free text. No controlled vocabulary applies.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>N/A | None</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Free text. No controlled vocabulary applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>N/A | None</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
           <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Keyed By (Rule 7)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>What the field's value repeats over</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Keyed By (Rule 7)</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>What the field's value repeats over</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Scalar — one value per procedure or analysis. The default.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>analyte</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Scalar — one value per procedure or analysis. The default.</t>
+          <t>One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>analyte</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>defines: analyte</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>defines: analyte</t>
+          <t>defines: channel per analyte</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per analyte. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>defines: channel per analyte</t>
+          <t>defines: reported property</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per analyte. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>defines: reported property</t>
+          <t>defines: sample</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
+          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>defines: sample</t>
+          <t>defines: sampling unit</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>defines: sampling unit</t>
+          <t>defines: standard</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reference material or reference database entry.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>defines: standard</t>
+          <t>reported property</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reference material or reference database entry.</t>
+          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>reported property</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
-        </is>
-      </c>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr"/>
+          <t>sample &gt; sampling unit</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>Nested — sampling unit exists only within sample. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>sample &gt; sampling unit</t>
+          <t>sample &gt; sampling unit x reported property</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Nested — sampling unit exists only within sample. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
+          <t>Cross-product, read as "for each sample, one value per reported property". One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume. + One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>sample &gt; sampling unit x reported property</t>
+          <t>standard x reported property</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>Cross-product, read as "for each sample, one value per reported property". One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume. + One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>standard x reported property</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>Cross-product, read as "for each standard, one value per reported property". One value per reference material or reference database entry. + One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
